--- a/90422_REPORT_BOTTEGA_04-01-2026.xlsx
+++ b/90422_REPORT_BOTTEGA_04-01-2026.xlsx
@@ -9,12 +9,13 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
+    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="53">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -49,6 +50,39 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
+    <t>16:00 - 16:59</t>
+  </si>
+  <si>
+    <t>17:00 - 17:59</t>
+  </si>
+  <si>
+    <t>18:00 - 18:59</t>
+  </si>
+  <si>
+    <t>19:00 - 19:59</t>
+  </si>
+  <si>
+    <t>20:00 - 20:59</t>
+  </si>
+  <si>
+    <t>21:00 - 21:59</t>
+  </si>
+  <si>
+    <t>22:00 - 22:59</t>
+  </si>
+  <si>
+    <t>23:00 - 23:59</t>
+  </si>
+  <si>
+    <t>0:00 - 0:59</t>
+  </si>
+  <si>
+    <t>1:00 - 1:59</t>
+  </si>
+  <si>
+    <t>2:00 - 2:59</t>
+  </si>
+  <si>
     <t>TOTALE INCASSI 04/01/2026</t>
   </si>
   <si>
@@ -125,6 +159,21 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>16:00-18:59</t>
+  </si>
+  <si>
+    <t>19:00-02:59</t>
+  </si>
+  <si>
+    <t>04/01/2026</t>
+  </si>
+  <si>
+    <t>VAR %</t>
+  </si>
+  <si>
+    <t>05/01/2025</t>
   </si>
 </sst>
 </file>
@@ -262,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -275,13 +324,27 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -369,27 +432,115 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="1">
+      <c r="A11" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="1">
-        <v>1005.09</v>
+      <c r="B11" t="n" s="5">
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="1">
+      <c r="A12" t="s" s="4">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="1">
-        <v>927.55</v>
+      <c r="B12" t="n" s="7">
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="1">
+      <c r="A13" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="1">
-        <v>8.36</v>
+      <c r="B13" t="n" s="5">
+        <v>2.7273</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="4">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n" s="7">
+        <v>61.9091</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n" s="5">
+        <v>188.9999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n" s="7">
+        <v>36.8183</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="4">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="B20" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B21" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B22" t="n" s="1">
+        <v>1295.55</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>23</v>
+      </c>
+      <c r="B23" t="n" s="1">
+        <v>1620.38</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B24" t="n" s="1">
+        <v>-20.05</v>
       </c>
     </row>
   </sheetData>
@@ -411,95 +562,95 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>481.4545</v>
+        <v>614.0</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>40.0</v>
+        <v>51.0</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>47.9</v>
+        <v>47.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>270.0</v>
+        <v>342.0</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>30.0</v>
+        <v>38.0</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>26.86</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>98.1818</v>
+        <v>159.5454</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>9.77</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>60.0001</v>
+        <v>84.5456</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>22.0</v>
+        <v>31.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>5.97</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>54.5454</v>
@@ -508,15 +659,15 @@
         <v>4.0</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>5.43</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n" s="5">
         <v>40.9091</v>
@@ -525,19 +676,19 @@
         <v>3.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>4.07</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="1">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" t="n" s="1">
-        <v>1005.09</v>
+        <v>1295.55</v>
       </c>
       <c r="D8" t="n" s="1">
-        <v>107.0</v>
+        <v>140.0</v>
       </c>
       <c r="E8" t="n" s="1">
         <v>100.0</v>
@@ -550,7 +701,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -561,13 +712,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -575,26 +726,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
       <c r="A5" t="s" s="1">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>40.0</v>
@@ -605,10 +756,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C7" t="n" s="5">
         <v>30.0</v>
@@ -619,10 +770,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C8" t="n" s="7">
         <v>22.0</v>
@@ -633,10 +784,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C9" t="n" s="5">
         <v>8.0</v>
@@ -647,10 +798,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>4.0</v>
@@ -661,10 +812,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>3.0</v>
@@ -675,10 +826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="1">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C12" t="n" s="1">
         <v>107.0</v>
@@ -688,13 +839,165 @@
       </c>
     </row>
     <row r="13"/>
+    <row r="14">
+      <c r="A14" t="s" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C15" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D15" t="n" s="5">
+        <v>2.7273</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="1">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s" s="4">
+        <v>47</v>
+      </c>
+      <c r="C16" t="n" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D16" t="n" s="1">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="s" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C19" t="n" s="5">
+        <v>11.0</v>
+      </c>
+      <c r="D19" t="n" s="5">
+        <v>132.5455</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="4">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s" s="4">
+        <v>33</v>
+      </c>
+      <c r="C20" t="n" s="7">
+        <v>8.0</v>
+      </c>
+      <c r="D20" t="n" s="7">
+        <v>72.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C21" t="n" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="D21" t="n" s="5">
+        <v>21.8182</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="C22" t="n" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="D22" t="n" s="7">
+        <v>61.3636</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C23" t="n" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="D23" t="n" s="1">
+        <v>287.73</v>
+      </c>
+    </row>
+    <row r="24"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="9">
+        <v>4482.0</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <f>(A2-C2)/C2</f>
+        <v>0.0</v>
+      </c>
+      <c r="C2" t="n" s="9">
+        <v>4653.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>